--- a/artfynd/A 42765-2022 artfynd.xlsx
+++ b/artfynd/A 42765-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42765-2022 artfynd.xlsx
+++ b/artfynd/A 42765-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106141179</v>
+        <v>79446674</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,46 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>5321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hasselbo, Vstm</t>
+          <t>Hasselbo (hagmark), Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560841.2386340753</v>
+        <v>560765</v>
       </c>
       <c r="R2" t="n">
-        <v>6617807.112596217</v>
+        <v>6617835</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -757,22 +743,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-01-24</t>
+          <t>2019-08-16</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-01-24</t>
+          <t>2019-08-16</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,18 +771,361 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Betesmark med asp, björk, sälg, rönn, lärk</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>79446162</v>
+      </c>
+      <c r="B3" t="n">
+        <v>111399</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219716</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Krusfrö</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Selinum carvifolia</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hasselbo (hagmark), Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>560765</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6617835</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2019-08-16</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2019-08-16</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Betesmark med asp, björk, sälg, rönn, lärk</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>5045114</v>
+      </c>
+      <c r="B4" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hasselbo (hagmark), Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>560765</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6617835</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2009-04-20</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2009-04-20</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Hagmark</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>106141179</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hasselbo, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>560842</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6617807</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2023-01-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2023-01-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Markus Rehnberg</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>Markus Rehnberg</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 42765-2022 artfynd.xlsx
+++ b/artfynd/A 42765-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79446674</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -914,6 +924,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79446162</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5045114</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,8 +1146,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106141179</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>